--- a/data/trans_dic/IP24_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que no hacen ejercicio</t>
+          <t>Menores que no hacen ejercicio (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,07; 30,4</t>
+          <t>17,0; 30,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,7; 28,4</t>
+          <t>14,23; 28,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,49; 27,94</t>
+          <t>13,39; 28,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,58; 18,93</t>
+          <t>8,56; 19,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,13; 33,63</t>
+          <t>18,26; 32,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,82; 23,65</t>
+          <t>10,98; 24,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,19; 31,13</t>
+          <t>18,43; 32,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,97; 23,84</t>
+          <t>12,24; 24,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,61; 29,06</t>
+          <t>19,68; 29,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,31; 24,43</t>
+          <t>14,5; 24,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,0; 28,14</t>
+          <t>17,8; 27,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,55; 19,77</t>
+          <t>11,73; 19,99</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,42; 32,63</t>
+          <t>17,03; 32,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 22,28</t>
+          <t>9,92; 22,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,87; 28,8</t>
+          <t>15,78; 28,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,05; 26,84</t>
+          <t>12,82; 27,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,05; 28,28</t>
+          <t>14,66; 28,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,37; 23,11</t>
+          <t>10,62; 23,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,5; 23,44</t>
+          <t>11,43; 22,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 18,34</t>
+          <t>7,45; 19,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,53; 27,59</t>
+          <t>17,82; 27,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,99; 20,29</t>
+          <t>11,7; 20,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,0; 23,64</t>
+          <t>15,3; 23,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,71; 20,79</t>
+          <t>11,94; 20,71</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,22; 32,08</t>
+          <t>15,48; 33,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,63; 31,61</t>
+          <t>16,19; 31,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,15; 32,74</t>
+          <t>15,88; 32,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,77; 25,82</t>
+          <t>8,86; 25,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,35; 27,43</t>
+          <t>13,53; 27,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,53; 23,36</t>
+          <t>10,22; 23,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,77; 21,52</t>
+          <t>8,18; 21,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,97; 26,6</t>
+          <t>7,77; 25,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,56; 26,55</t>
+          <t>16,59; 26,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,0; 24,95</t>
+          <t>14,75; 24,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,89; 24,22</t>
+          <t>13,24; 24,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,36; 24,26</t>
+          <t>10,07; 23,3</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,67; 30,65</t>
+          <t>21,0; 30,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 26,46</t>
+          <t>16,72; 25,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,14; 26,23</t>
+          <t>16,94; 25,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,02; 59,88</t>
+          <t>25,97; 63,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,64; 27,55</t>
+          <t>18,31; 27,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,55; 20,91</t>
+          <t>12,38; 20,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,87; 19,12</t>
+          <t>11,27; 19,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,45; 25,65</t>
+          <t>15,85; 25,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,84; 27,67</t>
+          <t>20,85; 27,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,53; 22,15</t>
+          <t>15,88; 22,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,01; 21,16</t>
+          <t>15,1; 21,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,31; 43,37</t>
+          <t>22,38; 44,35</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,89; 39,98</t>
+          <t>25,3; 40,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,91; 27,14</t>
+          <t>15,29; 26,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 25,29</t>
+          <t>14,59; 25,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,19; 21,68</t>
+          <t>11,07; 21,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,94; 27,74</t>
+          <t>16,25; 27,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,41; 22,28</t>
+          <t>11,04; 22,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,29; 20,03</t>
+          <t>10,6; 20,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,03; 39,28</t>
+          <t>14,12; 37,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,92; 30,93</t>
+          <t>21,98; 31,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,61; 22,25</t>
+          <t>14,2; 22,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,14; 21,2</t>
+          <t>13,44; 20,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 30,64</t>
+          <t>14,66; 30,41</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,76; 29,2</t>
+          <t>14,41; 29,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,53; 30,32</t>
+          <t>12,3; 30,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,29; 44,68</t>
+          <t>25,02; 44,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,53; 27,94</t>
+          <t>11,0; 28,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,83; 39,39</t>
+          <t>21,91; 39,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,32; 22,8</t>
+          <t>9,76; 24,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,75; 26,17</t>
+          <t>11,12; 26,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,41; 23,59</t>
+          <t>7,07; 21,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,11; 32,05</t>
+          <t>19,64; 31,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,53; 23,32</t>
+          <t>12,71; 23,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,7; 32,31</t>
+          <t>20,15; 32,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,23; 22,47</t>
+          <t>11,46; 22,68</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,23; 27,88</t>
+          <t>22,29; 28,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,99; 23,03</t>
+          <t>18,12; 23,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,82; 25,11</t>
+          <t>19,78; 24,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,84; 35,7</t>
+          <t>18,87; 33,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,5; 25,55</t>
+          <t>20,51; 25,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,11; 18,88</t>
+          <t>14,15; 18,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,54; 19,09</t>
+          <t>14,5; 18,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,32; 22,35</t>
+          <t>15,52; 22,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,28; 26,06</t>
+          <t>22,24; 25,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,44; 19,9</t>
+          <t>16,51; 19,96</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,74; 21,16</t>
+          <t>17,75; 21,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,9; 25,7</t>
+          <t>17,99; 26,98</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que no hacen ejercicio (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>24335</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18683</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16668</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13580</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>24380</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15093</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24736</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>23960</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>48715</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>33777</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>41404</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>37540</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>17738; 31465</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12802; 25697</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11122; 23545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8938; 20172</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17693; 31612</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9773; 21564</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>18273; 32091</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>16705; 33251</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>39609; 58728</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>25946; 43199</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>32435; 51010</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>28262; 48162</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>20871</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14483</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22615</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18071</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17413</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>15667</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18755</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>11959</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>38284</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>30149</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>41370</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>30030</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>14883; 28135</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9254; 20687</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16569; 29557</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>12065; 25567</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>12599; 24115</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>10140; 22261</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12815; 25528</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>7079; 18346</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>30889; 47657</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>22078; 38393</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>33229; 51389</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>22583; 39184</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>15406</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19440</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14607</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8372</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>20065</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13998</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10489</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9192</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>35471</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>33439</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>25096</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>17564</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10319; 22053</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13809; 26449</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9820; 20136</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4594; 13419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13442; 26944</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8817; 20128</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6119; 16033</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>4902; 15794</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>27543; 44574</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>25297; 42041</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18082; 32800</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>11577; 26781</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>51246</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>43830</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>47301</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>81405</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>46061</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>36778</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>30609</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>43994</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>97307</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>80607</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>77909</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>125399</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>42148; 61561</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>34165; 53074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37769; 57277</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>56365; 137835</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>37005; 55970</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>27767; 46620</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>23765; 40755</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>34251; 55324</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>84002; 110907</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>68055; 95459</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>65486; 91909</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>96923; 192110</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>33633</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>30063</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>26716</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>19238</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>27246</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22061</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>21025</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>35811</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>60879</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>52123</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>47741</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>55049</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>26345; 42238</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22356; 38562</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19868; 34779</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13223; 25952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>20566; 35396</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>15316; 31145</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14991; 29027</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>22904; 60805</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>50713; 72151</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>40467; 63494</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>37316; 57896</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>41279; 85656</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>15482</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10976</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>21148</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12687</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>22046</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>11570</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>12220</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>9443</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>37528</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>22546</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>33368</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>22130</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>10687; 21725</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>6632; 16309</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>15283; 27370</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>7577; 19808</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>15861; 28331</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>7225; 17992</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>7543; 17759</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>5089; 15496</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>28777; 45677</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>16268; 30350</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>25971; 42149</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>16142; 31957</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>160973</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>137475</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>149055</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>153353</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>157211</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>115167</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>117834</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>134359</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>318184</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>252642</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>266890</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>287712</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>142048; 180062</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>121897; 155632</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>132533; 166827</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>123778; 220506</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>140142; 175897</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100182; 132220</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>102424; 133593</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>115595; 167274</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>293717; 342875</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>228009; 275547</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>244326; 289216</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>252011; 377987</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP24_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,0; 30,15</t>
+          <t>17,38; 29,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,23; 28,57</t>
+          <t>14,18; 27,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,39; 28,34</t>
+          <t>13,35; 27,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,56; 19,31</t>
+          <t>8,14; 18,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,26; 32,63</t>
+          <t>18,67; 32,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,98; 24,24</t>
+          <t>11,1; 23,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,43; 32,37</t>
+          <t>18,6; 32,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,24; 24,36</t>
+          <t>11,78; 24,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,68; 29,18</t>
+          <t>19,65; 29,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,5; 24,15</t>
+          <t>14,45; 23,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,8; 27,99</t>
+          <t>17,99; 27,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,73; 19,99</t>
+          <t>11,55; 20,03</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,03; 32,19</t>
+          <t>17,39; 32,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,92; 22,18</t>
+          <t>10,58; 22,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,78; 28,14</t>
+          <t>15,98; 29,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,82; 27,17</t>
+          <t>12,86; 26,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,66; 28,05</t>
+          <t>14,1; 28,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,62; 23,32</t>
+          <t>10,96; 23,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,43; 22,77</t>
+          <t>11,53; 22,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 19,3</t>
+          <t>8,05; 20,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,82; 27,49</t>
+          <t>17,63; 27,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,7; 20,34</t>
+          <t>11,85; 20,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,3; 23,67</t>
+          <t>14,73; 23,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 20,71</t>
+          <t>11,8; 20,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,48; 33,08</t>
+          <t>15,18; 32,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,19; 31,02</t>
+          <t>15,5; 30,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,88; 32,56</t>
+          <t>16,12; 33,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,86; 25,87</t>
+          <t>9,09; 27,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,53; 27,13</t>
+          <t>14,18; 27,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,22; 23,34</t>
+          <t>10,25; 23,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 21,44</t>
+          <t>8,62; 21,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 25,04</t>
+          <t>7,63; 26,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,59; 26,85</t>
+          <t>16,87; 27,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 24,51</t>
+          <t>15,33; 25,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,24; 24,01</t>
+          <t>13,41; 23,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 23,3</t>
+          <t>10,26; 22,87</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,0; 30,67</t>
+          <t>20,95; 30,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,72; 25,98</t>
+          <t>16,93; 26,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,94; 25,7</t>
+          <t>17,13; 25,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,97; 63,5</t>
+          <t>25,77; 59,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,31; 27,7</t>
+          <t>18,18; 27,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,38; 20,78</t>
+          <t>12,1; 20,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,27; 19,33</t>
+          <t>10,82; 19,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,85; 25,6</t>
+          <t>15,54; 25,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,85; 27,53</t>
+          <t>20,67; 27,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,88; 22,27</t>
+          <t>16,12; 22,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,1; 21,19</t>
+          <t>15,0; 20,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,38; 44,35</t>
+          <t>22,55; 43,03</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,3; 40,57</t>
+          <t>25,19; 40,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,29; 26,38</t>
+          <t>15,59; 26,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,59; 25,54</t>
+          <t>14,54; 25,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,07; 21,73</t>
+          <t>11,26; 21,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,25; 27,96</t>
+          <t>16,45; 28,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 22,44</t>
+          <t>11,29; 22,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,6; 20,52</t>
+          <t>10,11; 20,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,12; 37,48</t>
+          <t>14,29; 38,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,98; 31,27</t>
+          <t>21,96; 31,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,2; 22,28</t>
+          <t>14,94; 22,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,44; 20,85</t>
+          <t>13,78; 21,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,66; 30,41</t>
+          <t>14,58; 29,37</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,41; 29,3</t>
+          <t>13,89; 28,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,3; 30,25</t>
+          <t>12,3; 29,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,02; 44,8</t>
+          <t>25,24; 45,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,0; 28,75</t>
+          <t>11,09; 28,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,91; 39,14</t>
+          <t>22,28; 40,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,76; 24,3</t>
+          <t>9,65; 23,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,12; 26,18</t>
+          <t>10,83; 25,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,07; 21,52</t>
+          <t>7,48; 21,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,64; 31,17</t>
+          <t>19,89; 31,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,71; 23,72</t>
+          <t>12,55; 23,38</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20,15; 32,7</t>
+          <t>19,89; 32,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,46; 22,68</t>
+          <t>10,96; 21,97</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,29; 28,25</t>
+          <t>22,53; 28,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,12; 23,13</t>
+          <t>18,15; 23,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,78; 24,89</t>
+          <t>19,45; 24,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,87; 33,62</t>
+          <t>19,02; 33,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,51; 25,74</t>
+          <t>20,62; 25,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,15; 18,68</t>
+          <t>13,9; 18,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,5; 18,92</t>
+          <t>14,51; 18,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,52; 22,45</t>
+          <t>15,38; 22,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,24; 25,96</t>
+          <t>22,32; 25,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,51; 19,96</t>
+          <t>16,66; 19,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,75; 21,01</t>
+          <t>17,79; 21,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,99; 26,98</t>
+          <t>17,75; 26,46</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17738; 31465</t>
+          <t>18137; 31292</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12802; 25697</t>
+          <t>12755; 25087</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11122; 23545</t>
+          <t>11091; 23093</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8938; 20172</t>
+          <t>8507; 19492</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17693; 31612</t>
+          <t>18094; 31687</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9773; 21564</t>
+          <t>9878; 21291</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18273; 32091</t>
+          <t>18440; 32361</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16705; 33251</t>
+          <t>16082; 32882</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39609; 58728</t>
+          <t>39537; 58925</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25946; 43199</t>
+          <t>25860; 42333</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32435; 51010</t>
+          <t>32790; 50300</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28262; 48162</t>
+          <t>27840; 48263</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14883; 28135</t>
+          <t>15193; 28448</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9254; 20687</t>
+          <t>9869; 21361</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16569; 29557</t>
+          <t>16788; 30642</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12065; 25567</t>
+          <t>12100; 24889</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12599; 24115</t>
+          <t>12122; 24144</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10140; 22261</t>
+          <t>10467; 22078</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12815; 25528</t>
+          <t>12921; 25635</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7079; 18346</t>
+          <t>7653; 19393</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30889; 47657</t>
+          <t>30565; 48052</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22078; 38393</t>
+          <t>22371; 38719</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33229; 51389</t>
+          <t>31987; 50934</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22583; 39184</t>
+          <t>22312; 39586</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10319; 22053</t>
+          <t>10119; 21408</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13809; 26449</t>
+          <t>13218; 25766</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9820; 20136</t>
+          <t>9966; 20995</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4594; 13419</t>
+          <t>4715; 14095</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13442; 26944</t>
+          <t>14087; 27424</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8817; 20128</t>
+          <t>8844; 20356</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6119; 16033</t>
+          <t>6446; 16427</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4902; 15794</t>
+          <t>4816; 16504</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27543; 44574</t>
+          <t>28004; 45691</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25297; 42041</t>
+          <t>26288; 43636</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18082; 32800</t>
+          <t>18322; 32410</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11577; 26781</t>
+          <t>11791; 26283</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42148; 61561</t>
+          <t>42061; 61913</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34165; 53074</t>
+          <t>34594; 53808</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37769; 57277</t>
+          <t>38179; 56831</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56365; 137835</t>
+          <t>55946; 128830</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37005; 55970</t>
+          <t>36745; 56357</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27767; 46620</t>
+          <t>27154; 45750</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23765; 40755</t>
+          <t>22818; 40099</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34251; 55324</t>
+          <t>33578; 55155</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84002; 110907</t>
+          <t>83257; 111493</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68055; 95459</t>
+          <t>69123; 95710</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65486; 91909</t>
+          <t>65086; 90008</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>96923; 192110</t>
+          <t>97663; 186384</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26345; 42238</t>
+          <t>26225; 41782</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22356; 38562</t>
+          <t>22784; 38613</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19868; 34779</t>
+          <t>19809; 34549</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13223; 25952</t>
+          <t>13448; 26074</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20566; 35396</t>
+          <t>20824; 35906</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15316; 31145</t>
+          <t>15672; 30934</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14991; 29027</t>
+          <t>14301; 28649</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22904; 60805</t>
+          <t>23189; 62160</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50713; 72151</t>
+          <t>50655; 71946</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40467; 63494</t>
+          <t>42567; 62707</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37316; 57896</t>
+          <t>38264; 59375</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>41279; 85656</t>
+          <t>41066; 82708</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10687; 21725</t>
+          <t>10297; 20926</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6632; 16309</t>
+          <t>6631; 16101</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15283; 27370</t>
+          <t>15418; 27542</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7577; 19808</t>
+          <t>7642; 19893</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15861; 28331</t>
+          <t>16126; 29024</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7225; 17992</t>
+          <t>7143; 17186</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7543; 17759</t>
+          <t>7346; 17533</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5089; 15496</t>
+          <t>5383; 15643</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28777; 45677</t>
+          <t>29154; 46675</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16268; 30350</t>
+          <t>16061; 29914</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25971; 42149</t>
+          <t>25639; 42136</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16142; 31957</t>
+          <t>15438; 30949</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>142048; 180062</t>
+          <t>143630; 178845</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>121897; 155632</t>
+          <t>122154; 156312</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>132533; 166827</t>
+          <t>130334; 165744</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>123778; 220506</t>
+          <t>124752; 219731</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>140142; 175897</t>
+          <t>140896; 177216</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>100182; 132220</t>
+          <t>98367; 132051</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>102424; 133593</t>
+          <t>102484; 133676</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>115595; 167274</t>
+          <t>114558; 166192</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>293717; 342875</t>
+          <t>294826; 343276</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>228009; 275547</t>
+          <t>229971; 275209</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>244326; 289216</t>
+          <t>244849; 292397</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>252011; 377987</t>
+          <t>248633; 370675</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP24_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25,16%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16,96%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17,52%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>23,32%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>20,77%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>20,06%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,95%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,38; 29,99</t>
+          <t>19,13; 33,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,18; 27,89</t>
+          <t>10,82; 23,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,35; 27,79</t>
+          <t>18,19; 31,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 18,66</t>
+          <t>11,65; 23,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,67; 32,7</t>
+          <t>17,07; 30,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,1; 23,93</t>
+          <t>14,7; 28,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,6; 32,64</t>
+          <t>13,49; 27,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,78; 24,09</t>
+          <t>8,07; 17,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,65; 29,28</t>
+          <t>19,61; 29,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,45; 23,66</t>
+          <t>14,31; 24,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,99; 27,6</t>
+          <t>18,0; 28,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,55; 20,03</t>
+          <t>11,28; 19,25</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,26%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16,41%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16,73%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,03%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>23,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>15,53%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>21,53%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,2%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>20,26%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,73%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,39; 32,55</t>
+          <t>14,05; 28,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,58; 22,9</t>
+          <t>10,37; 23,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,98; 29,18</t>
+          <t>11,5; 23,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,86; 26,45</t>
+          <t>7,44; 17,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,1; 28,08</t>
+          <t>17,42; 32,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,96; 23,13</t>
+          <t>9,79; 22,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,53; 22,87</t>
+          <t>15,87; 28,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,05; 20,4</t>
+          <t>12,65; 27,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,63; 27,72</t>
+          <t>17,53; 27,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 20,51</t>
+          <t>11,99; 20,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,73; 23,46</t>
+          <t>15,0; 23,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,8; 20,93</t>
+          <t>11,3; 20,3</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,2%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14,03%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10,96%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>23,11%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>22,8%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>23,62%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16,14%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,2%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,18; 32,12</t>
+          <t>14,35; 27,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,5; 30,22</t>
+          <t>10,53; 23,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,12; 33,95</t>
+          <t>8,77; 21,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,09; 27,18</t>
+          <t>6,14; 18,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,18; 27,61</t>
+          <t>15,22; 32,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 23,6</t>
+          <t>16,63; 31,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,62; 21,97</t>
+          <t>15,15; 32,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 26,16</t>
+          <t>7,73; 24,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,87; 27,53</t>
+          <t>16,56; 26,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,33; 25,44</t>
+          <t>15,0; 24,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,41; 23,72</t>
+          <t>13,89; 24,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,26; 22,87</t>
+          <t>8,8; 19,87</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22,79%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16,39%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14,52%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>25,53%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>21,45%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>21,22%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>37,5%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,79%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,52%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,95; 30,84</t>
+          <t>18,64; 27,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,93; 26,33</t>
+          <t>12,55; 20,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,13; 25,5</t>
+          <t>10,87; 19,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,77; 59,35</t>
+          <t>14,26; 23,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,18; 27,89</t>
+          <t>20,67; 30,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,1; 20,39</t>
+          <t>17,26; 26,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 19,02</t>
+          <t>17,14; 26,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,54; 25,53</t>
+          <t>19,49; 30,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,67; 27,68</t>
+          <t>20,84; 27,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,12; 22,33</t>
+          <t>15,53; 22,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,0; 20,75</t>
+          <t>15,01; 21,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,55; 43,03</t>
+          <t>18,12; 25,3</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21,52%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15,9%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19,82%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>32,3%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>20,57%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>19,62%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>21,52%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,19; 40,13</t>
+          <t>15,94; 27,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,59; 26,41</t>
+          <t>11,41; 22,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,54; 25,37</t>
+          <t>10,29; 20,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,26; 21,83</t>
+          <t>12,54; 35,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,45; 28,36</t>
+          <t>25,89; 39,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,29; 22,29</t>
+          <t>15,91; 27,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,11; 20,26</t>
+          <t>14,46; 25,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,29; 38,32</t>
+          <t>10,18; 19,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,96; 31,18</t>
+          <t>21,92; 30,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,94; 22,01</t>
+          <t>14,61; 22,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,78; 21,39</t>
+          <t>14,14; 21,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 29,37</t>
+          <t>13,14; 27,77</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>30,45%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15,63%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12,21%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>20,88%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>20,36%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>34,62%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18,41%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>30,45%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,89; 28,22</t>
+          <t>21,83; 39,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,3; 29,87</t>
+          <t>9,32; 22,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,24; 45,09</t>
+          <t>10,75; 26,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 28,87</t>
+          <t>6,79; 21,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,28; 40,09</t>
+          <t>14,76; 29,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,65; 23,21</t>
+          <t>12,53; 30,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,83; 25,85</t>
+          <t>25,29; 44,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,48; 21,72</t>
+          <t>9,06; 23,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,89; 31,85</t>
+          <t>20,11; 32,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,55; 23,38</t>
+          <t>12,53; 23,32</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,89; 32,69</t>
+          <t>19,7; 32,31</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,96; 21,97</t>
+          <t>9,81; 19,56</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16,27%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16,69%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16,69%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>25,25%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>20,43%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>22,24%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>23,38%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>23,01%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,69%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,53; 28,06</t>
+          <t>20,5; 25,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,15; 23,23</t>
+          <t>14,11; 18,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,45; 24,73</t>
+          <t>14,54; 19,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,02; 33,5</t>
+          <t>14,19; 20,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,62; 25,94</t>
+          <t>22,23; 27,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,9; 18,65</t>
+          <t>17,99; 23,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,51; 18,93</t>
+          <t>19,82; 25,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,38; 22,31</t>
+          <t>15,34; 20,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,32; 25,99</t>
+          <t>22,28; 26,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,66; 19,93</t>
+          <t>16,44; 19,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,79; 21,25</t>
+          <t>17,74; 21,16</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,75; 26,46</t>
+          <t>15,29; 19,25</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24380</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15093</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24736</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21423</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>24335</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>18683</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>16668</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13580</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>24380</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15093</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>24736</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23960</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37540</t>
+          <t>34206</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18137; 31292</t>
+          <t>18536; 32588</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12755; 25087</t>
+          <t>9631; 21039</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11091; 23093</t>
+          <t>18039; 30864</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8507; 19492</t>
+          <t>14246; 28744</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18094; 31687</t>
+          <t>17816; 31723</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9878; 21291</t>
+          <t>13219; 25540</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18440; 32361</t>
+          <t>11207; 23217</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16082; 32882</t>
+          <t>8303; 18415</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39537; 58925</t>
+          <t>39467; 58482</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25860; 42333</t>
+          <t>25595; 43714</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32790; 50300</t>
+          <t>32801; 51288</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27840; 48263</t>
+          <t>25410; 43348</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17413</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15667</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18755</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10943</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>20871</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14483</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>22615</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18071</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17413</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15667</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18755</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11959</t>
+          <t>17985</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30030</t>
+          <t>28928</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15193; 28448</t>
+          <t>12080; 24310</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9869; 21361</t>
+          <t>9900; 22060</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16788; 30642</t>
+          <t>12894; 26276</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12100; 24889</t>
+          <t>6765; 16175</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12122; 24144</t>
+          <t>15223; 28512</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10467; 22078</t>
+          <t>9134; 20779</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12921; 25635</t>
+          <t>16665; 30243</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7653; 19393</t>
+          <t>12153; 26065</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30565; 48052</t>
+          <t>30392; 47824</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22371; 38719</t>
+          <t>22626; 38295</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31987; 50934</t>
+          <t>32571; 51326</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22312; 39586</t>
+          <t>21129; 37967</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>20065</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13998</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10489</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6169</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>15406</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>19440</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>14607</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8372</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>20065</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13998</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10489</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>14124</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10119; 21408</t>
+          <t>14252; 27243</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13218; 25766</t>
+          <t>9083; 20150</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9966; 20995</t>
+          <t>6556; 16093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4715; 14095</t>
+          <t>3455; 10448</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14087; 27424</t>
+          <t>10148; 21386</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8844; 20356</t>
+          <t>14181; 26952</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6446; 16427</t>
+          <t>9371; 20245</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4816; 16504</t>
+          <t>4135; 12869</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28004; 45691</t>
+          <t>27496; 44071</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26288; 43636</t>
+          <t>25735; 42797</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18322; 32410</t>
+          <t>18970; 33087</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11791; 26283</t>
+          <t>9665; 21812</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>68</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46061</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36778</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30609</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38257</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>51246</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>43830</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>47301</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>81405</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>46061</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>36778</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30609</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>43994</t>
+          <t>43246</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>125399</t>
+          <t>81504</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42061; 61913</t>
+          <t>37675; 55674</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34594; 53808</t>
+          <t>28159; 46919</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38179; 56831</t>
+          <t>22922; 40322</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55946; 128830</t>
+          <t>28517; 47798</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36745; 56357</t>
+          <t>41489; 61534</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27154; 45750</t>
+          <t>35259; 54056</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22818; 40099</t>
+          <t>38211; 58473</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33578; 55155</t>
+          <t>34687; 54297</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83257; 111493</t>
+          <t>83929; 111469</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69123; 95710</t>
+          <t>66561; 94949</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65086; 90008</t>
+          <t>65096; 91797</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>97663; 186384</t>
+          <t>68506; 95632</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>27246</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22061</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21025</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29317</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>33633</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>30063</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>26716</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>19238</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>27246</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22061</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21025</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35811</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55049</t>
+          <t>46882</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26225; 41782</t>
+          <t>20178; 35120</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22784; 38613</t>
+          <t>15829; 30916</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19809; 34549</t>
+          <t>14555; 28325</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13448; 26074</t>
+          <t>18548; 52861</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20824; 35906</t>
+          <t>26953; 41628</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15672; 30934</t>
+          <t>23252; 39668</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14301; 28649</t>
+          <t>19700; 34443</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23189; 62160</t>
+          <t>12082; 23697</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50655; 71946</t>
+          <t>50569; 71347</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42567; 62707</t>
+          <t>41639; 63397</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38264; 59375</t>
+          <t>39251; 58866</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>41066; 82708</t>
+          <t>35052; 74051</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>22046</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11570</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>12220</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8341</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>15482</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>10976</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>21148</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>12687</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>22046</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>11570</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>12220</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>10703</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22130</t>
+          <t>19045</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10297; 20926</t>
+          <t>15804; 28516</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6631; 16101</t>
+          <t>6901; 16878</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15418; 27542</t>
+          <t>7289; 17751</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7642; 19893</t>
+          <t>4638; 14731</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16126; 29024</t>
+          <t>10948; 21648</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7143; 17186</t>
+          <t>6754; 16344</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7346; 17533</t>
+          <t>15447; 27292</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5383; 15643</t>
+          <t>6377; 16331</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29154; 46675</t>
+          <t>29469; 46960</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16061; 29914</t>
+          <t>16030; 29832</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25639; 42136</t>
+          <t>25393; 41649</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15438; 30949</t>
+          <t>13598; 27118</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>229</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>181</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>157211</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>115167</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>117834</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>114450</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>160973</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>137475</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>149055</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>153353</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>157211</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>115167</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>117834</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>134359</t>
+          <t>110239</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>287712</t>
+          <t>224688</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>143630; 178845</t>
+          <t>140093; 174544</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>122154; 156312</t>
+          <t>99847; 133666</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>130334; 165744</t>
+          <t>102647; 134776</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>124752; 219731</t>
+          <t>97321; 143076</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>140896; 177216</t>
+          <t>141709; 177719</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>98367; 132051</t>
+          <t>121080; 154955</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>102484; 133676</t>
+          <t>132843; 168306</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>114558; 166192</t>
+          <t>95016; 126736</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>294826; 343276</t>
+          <t>294201; 344207</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>229971; 275209</t>
+          <t>227044; 274832</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>244849; 292397</t>
+          <t>244150; 291175</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>248633; 370675</t>
+          <t>199585; 251283</t>
         </is>
       </c>
     </row>
